--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="579">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1727,6 +1727,30 @@
   </si>
   <si>
     <t>[{"altitude_ft":62992.0,"altitude_m":19199.96,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-04-12</t>
+  </si>
+  <si>
+    <t>EOSS-394</t>
+  </si>
+  <si>
+    <t>2hrs 7mins 30secs</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":41952.0,"altitude_m":12786.97,"transition":"high_to_low"},{"altitude_ft":54733.0,"altitude_m":16682.62,"transition":"low_to_high"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-2","K0SCC-13","AE0SS-4"]</t>
+  </si>
+  <si>
+    <t>EOSS-395</t>
+  </si>
+  <si>
+    <t>1hrs 55mins 29secs</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":12263.0,"altitude_m":3737.76,"transition":"low_to_high"},{"altitude_ft":64144.0,"altitude_m":19551.09,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2058,7 +2082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT104"/>
+  <dimension ref="A1:AT106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -16621,6 +16645,286 @@
         <v>1.75</v>
       </c>
     </row>
+    <row r="105" spans="1:46">
+      <c r="A105" t="s">
+        <v>62</v>
+      </c>
+      <c r="B105" t="s">
+        <v>566</v>
+      </c>
+      <c r="C105" t="s">
+        <v>571</v>
+      </c>
+      <c r="D105">
+        <v>91837</v>
+      </c>
+      <c r="E105">
+        <v>27991.92</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>572</v>
+      </c>
+      <c r="H105" t="s">
+        <v>573</v>
+      </c>
+      <c r="I105">
+        <v>7650</v>
+      </c>
+      <c r="J105" t="s">
+        <v>372</v>
+      </c>
+      <c r="K105">
+        <v>4595</v>
+      </c>
+      <c r="L105">
+        <v>1400.56</v>
+      </c>
+      <c r="M105">
+        <v>90.57</v>
+      </c>
+      <c r="N105">
+        <v>56.28</v>
+      </c>
+      <c r="O105">
+        <v>40.01166666666666</v>
+      </c>
+      <c r="P105">
+        <v>-103.12033333333332</v>
+      </c>
+      <c r="Q105">
+        <v>5216</v>
+      </c>
+      <c r="R105">
+        <v>1589.84</v>
+      </c>
+      <c r="S105">
+        <v>39.608</v>
+      </c>
+      <c r="T105">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U105" t="s">
+        <v>118</v>
+      </c>
+      <c r="V105">
+        <v>91612</v>
+      </c>
+      <c r="W105">
+        <v>27923.34</v>
+      </c>
+      <c r="X105">
+        <v>302</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z105">
+        <v>12</v>
+      </c>
+      <c r="AA105">
+        <v>3.66</v>
+      </c>
+      <c r="AB105">
+        <v>0.79</v>
+      </c>
+      <c r="AC105">
+        <v>1.75</v>
+      </c>
+      <c r="AD105">
+        <v>90.57</v>
+      </c>
+      <c r="AE105">
+        <v>56.28</v>
+      </c>
+      <c r="AF105" t="s">
+        <v>574</v>
+      </c>
+      <c r="AG105">
+        <v>1.5</v>
+      </c>
+      <c r="AH105">
+        <v>3.31</v>
+      </c>
+      <c r="AI105">
+        <v>3.46</v>
+      </c>
+      <c r="AJ105">
+        <v>7.62</v>
+      </c>
+      <c r="AK105">
+        <v>1.65</v>
+      </c>
+      <c r="AL105">
+        <v>3.64</v>
+      </c>
+      <c r="AM105">
+        <v>7.4</v>
+      </c>
+      <c r="AN105">
+        <v>16.32</v>
+      </c>
+      <c r="AO105">
+        <v>8.12</v>
+      </c>
+      <c r="AP105">
+        <v>17.91</v>
+      </c>
+      <c r="AQ105">
+        <v>5.9</v>
+      </c>
+      <c r="AR105">
+        <v>13.01</v>
+      </c>
+      <c r="AS105">
+        <v>0.79</v>
+      </c>
+      <c r="AT105">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="106" spans="1:46">
+      <c r="A106" t="s">
+        <v>46</v>
+      </c>
+      <c r="B106" t="s">
+        <v>575</v>
+      </c>
+      <c r="C106" t="s">
+        <v>571</v>
+      </c>
+      <c r="D106">
+        <v>99167</v>
+      </c>
+      <c r="E106">
+        <v>30226.1</v>
+      </c>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>576</v>
+      </c>
+      <c r="H106" t="s">
+        <v>577</v>
+      </c>
+      <c r="I106">
+        <v>6929</v>
+      </c>
+      <c r="J106" t="s">
+        <v>263</v>
+      </c>
+      <c r="K106">
+        <v>4617</v>
+      </c>
+      <c r="L106">
+        <v>1407.26</v>
+      </c>
+      <c r="M106">
+        <v>85.13</v>
+      </c>
+      <c r="N106">
+        <v>52.9</v>
+      </c>
+      <c r="O106">
+        <v>39.89648333333333</v>
+      </c>
+      <c r="P106">
+        <v>-103.11896666666668</v>
+      </c>
+      <c r="Q106">
+        <v>5211</v>
+      </c>
+      <c r="R106">
+        <v>1588.31</v>
+      </c>
+      <c r="S106">
+        <v>39.608</v>
+      </c>
+      <c r="T106">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U106" t="s">
+        <v>156</v>
+      </c>
+      <c r="V106">
+        <v>99059</v>
+      </c>
+      <c r="W106">
+        <v>30193.18</v>
+      </c>
+      <c r="X106">
+        <v>353</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z106">
+        <v>12</v>
+      </c>
+      <c r="AA106">
+        <v>3.66</v>
+      </c>
+      <c r="AB106">
+        <v>0.77</v>
+      </c>
+      <c r="AC106">
+        <v>1.7</v>
+      </c>
+      <c r="AD106">
+        <v>85.13</v>
+      </c>
+      <c r="AE106">
+        <v>52.9</v>
+      </c>
+      <c r="AF106" t="s">
+        <v>578</v>
+      </c>
+      <c r="AG106">
+        <v>3</v>
+      </c>
+      <c r="AH106">
+        <v>6.61</v>
+      </c>
+      <c r="AI106">
+        <v>7.02</v>
+      </c>
+      <c r="AJ106">
+        <v>15.47</v>
+      </c>
+      <c r="AK106">
+        <v>2.08</v>
+      </c>
+      <c r="AL106">
+        <v>4.58</v>
+      </c>
+      <c r="AM106">
+        <v>12.86</v>
+      </c>
+      <c r="AN106">
+        <v>28.36</v>
+      </c>
+      <c r="AO106">
+        <v>12.44</v>
+      </c>
+      <c r="AP106">
+        <v>27.42</v>
+      </c>
+      <c r="AQ106">
+        <v>9.87</v>
+      </c>
+      <c r="AR106">
+        <v>21.75</v>
+      </c>
+      <c r="AS106">
+        <v>0.77</v>
+      </c>
+      <c r="AT106">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="588">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1751,6 +1751,33 @@
   </si>
   <si>
     <t>[{"altitude_ft":12263.0,"altitude_m":3737.76,"transition":"low_to_high"},{"altitude_ft":64144.0,"altitude_m":19551.09,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-04-19</t>
+  </si>
+  <si>
+    <t>EOSS-396</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":37233.0,"altitude_m":11348.62,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["AE0SS-1","K0SCC-13","AE0SS-3"]</t>
+  </si>
+  <si>
+    <t>EOSS-397</t>
+  </si>
+  <si>
+    <t>2hrs 19mins 30secs</t>
+  </si>
+  <si>
+    <t>396</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":36584.0,"altitude_m":11150.8,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2082,7 +2109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT106"/>
+  <dimension ref="A1:AT108"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -16925,6 +16952,286 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="107" spans="1:46">
+      <c r="A107" t="s">
+        <v>46</v>
+      </c>
+      <c r="B107" t="s">
+        <v>552</v>
+      </c>
+      <c r="C107" t="s">
+        <v>579</v>
+      </c>
+      <c r="D107">
+        <v>84042</v>
+      </c>
+      <c r="E107">
+        <v>25616</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>580</v>
+      </c>
+      <c r="H107" t="s">
+        <v>568</v>
+      </c>
+      <c r="I107">
+        <v>7230</v>
+      </c>
+      <c r="J107" t="s">
+        <v>581</v>
+      </c>
+      <c r="K107">
+        <v>4468</v>
+      </c>
+      <c r="L107">
+        <v>1361.85</v>
+      </c>
+      <c r="M107">
+        <v>140.9</v>
+      </c>
+      <c r="N107">
+        <v>87.55</v>
+      </c>
+      <c r="O107">
+        <v>39.20616666666667</v>
+      </c>
+      <c r="P107">
+        <v>-102.48566666666666</v>
+      </c>
+      <c r="Q107">
+        <v>5214</v>
+      </c>
+      <c r="R107">
+        <v>1589.23</v>
+      </c>
+      <c r="S107">
+        <v>39.608</v>
+      </c>
+      <c r="T107">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U107" t="s">
+        <v>156</v>
+      </c>
+      <c r="V107">
+        <v>83849</v>
+      </c>
+      <c r="W107">
+        <v>25557.18</v>
+      </c>
+      <c r="X107">
+        <v>251</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z107">
+        <v>12</v>
+      </c>
+      <c r="AA107">
+        <v>3.66</v>
+      </c>
+      <c r="AB107">
+        <v>0.77</v>
+      </c>
+      <c r="AC107">
+        <v>1.7</v>
+      </c>
+      <c r="AD107">
+        <v>140.9</v>
+      </c>
+      <c r="AE107">
+        <v>87.55</v>
+      </c>
+      <c r="AF107" t="s">
+        <v>582</v>
+      </c>
+      <c r="AG107">
+        <v>3</v>
+      </c>
+      <c r="AH107">
+        <v>6.61</v>
+      </c>
+      <c r="AI107">
+        <v>4.75</v>
+      </c>
+      <c r="AJ107">
+        <v>10.48</v>
+      </c>
+      <c r="AK107">
+        <v>1.53</v>
+      </c>
+      <c r="AL107">
+        <v>3.38</v>
+      </c>
+      <c r="AM107">
+        <v>10.06</v>
+      </c>
+      <c r="AN107">
+        <v>22.17</v>
+      </c>
+      <c r="AO107">
+        <v>9.07</v>
+      </c>
+      <c r="AP107">
+        <v>19.99</v>
+      </c>
+      <c r="AQ107">
+        <v>7.06</v>
+      </c>
+      <c r="AR107">
+        <v>15.56</v>
+      </c>
+      <c r="AS107">
+        <v>0.77</v>
+      </c>
+      <c r="AT107">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:46">
+      <c r="A108" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" t="s">
+        <v>583</v>
+      </c>
+      <c r="C108" t="s">
+        <v>579</v>
+      </c>
+      <c r="D108">
+        <v>96668</v>
+      </c>
+      <c r="E108">
+        <v>29464.41</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>584</v>
+      </c>
+      <c r="H108" t="s">
+        <v>585</v>
+      </c>
+      <c r="I108">
+        <v>8370</v>
+      </c>
+      <c r="J108" t="s">
+        <v>586</v>
+      </c>
+      <c r="K108">
+        <v>5253</v>
+      </c>
+      <c r="L108">
+        <v>1601.11</v>
+      </c>
+      <c r="M108">
+        <v>166.37</v>
+      </c>
+      <c r="N108">
+        <v>103.38</v>
+      </c>
+      <c r="O108">
+        <v>39.13243333333334</v>
+      </c>
+      <c r="P108">
+        <v>-102.20588333333332</v>
+      </c>
+      <c r="Q108">
+        <v>5224</v>
+      </c>
+      <c r="R108">
+        <v>1592.28</v>
+      </c>
+      <c r="S108">
+        <v>39.6082</v>
+      </c>
+      <c r="T108">
+        <v>-104.0423</v>
+      </c>
+      <c r="U108" t="s">
+        <v>156</v>
+      </c>
+      <c r="V108">
+        <v>96417</v>
+      </c>
+      <c r="W108">
+        <v>29387.9</v>
+      </c>
+      <c r="X108">
+        <v>800</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z108">
+        <v>12</v>
+      </c>
+      <c r="AA108">
+        <v>3.66</v>
+      </c>
+      <c r="AB108">
+        <v>0.82</v>
+      </c>
+      <c r="AC108">
+        <v>1.81</v>
+      </c>
+      <c r="AD108">
+        <v>166.37</v>
+      </c>
+      <c r="AE108">
+        <v>103.38</v>
+      </c>
+      <c r="AF108" t="s">
+        <v>587</v>
+      </c>
+      <c r="AG108">
+        <v>3</v>
+      </c>
+      <c r="AH108">
+        <v>6.61</v>
+      </c>
+      <c r="AI108">
+        <v>5.06</v>
+      </c>
+      <c r="AJ108">
+        <v>11.15</v>
+      </c>
+      <c r="AK108">
+        <v>2.2</v>
+      </c>
+      <c r="AL108">
+        <v>4.84</v>
+      </c>
+      <c r="AM108">
+        <v>11.07</v>
+      </c>
+      <c r="AN108">
+        <v>24.41</v>
+      </c>
+      <c r="AO108">
+        <v>10.29</v>
+      </c>
+      <c r="AP108">
+        <v>22.68</v>
+      </c>
+      <c r="AQ108">
+        <v>8.07</v>
+      </c>
+      <c r="AR108">
+        <v>17.8</v>
+      </c>
+      <c r="AS108">
+        <v>0.82</v>
+      </c>
+      <c r="AT108">
+        <v>1.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="602">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1778,6 +1778,48 @@
   </si>
   <si>
     <t>[{"altitude_ft":36584.0,"altitude_m":11150.8,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-2","K0SCC-13"]</t>
+  </si>
+  <si>
+    <t>2026-05-02</t>
+  </si>
+  <si>
+    <t>EOSS-398</t>
+  </si>
+  <si>
+    <t>1hrs 48mins 30secs</t>
+  </si>
+  <si>
+    <t>293</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":52824.0,"altitude_m":16100.76,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-3","AE0SS-3"]</t>
+  </si>
+  <si>
+    <t>EOSS-399</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":46553.0,"altitude_m":14189.35,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-14","AE0SS-4","K0SCC-14"]</t>
+  </si>
+  <si>
+    <t>EOSS-400</t>
+  </si>
+  <si>
+    <t>2hrs 13mins 0secs</t>
+  </si>
+  <si>
+    <t>316</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":41058.0,"altitude_m":12514.48,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2151,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT108"/>
+  <dimension ref="A1:AT111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -17232,6 +17274,426 @@
         <v>1.81</v>
       </c>
     </row>
+    <row r="109" spans="1:46">
+      <c r="A109" t="s">
+        <v>62</v>
+      </c>
+      <c r="B109" t="s">
+        <v>588</v>
+      </c>
+      <c r="C109" t="s">
+        <v>589</v>
+      </c>
+      <c r="D109">
+        <v>89253</v>
+      </c>
+      <c r="E109">
+        <v>27204.31</v>
+      </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>590</v>
+      </c>
+      <c r="H109" t="s">
+        <v>591</v>
+      </c>
+      <c r="I109">
+        <v>6510</v>
+      </c>
+      <c r="J109" t="s">
+        <v>592</v>
+      </c>
+      <c r="K109">
+        <v>7525</v>
+      </c>
+      <c r="L109">
+        <v>2293.62</v>
+      </c>
+      <c r="M109">
+        <v>54.17</v>
+      </c>
+      <c r="N109">
+        <v>33.66</v>
+      </c>
+      <c r="O109">
+        <v>39.27166666666667</v>
+      </c>
+      <c r="P109">
+        <v>-103.58533333333334</v>
+      </c>
+      <c r="Q109">
+        <v>5222</v>
+      </c>
+      <c r="R109">
+        <v>1591.67</v>
+      </c>
+      <c r="S109">
+        <v>39.608</v>
+      </c>
+      <c r="T109">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U109" t="s">
+        <v>118</v>
+      </c>
+      <c r="V109">
+        <v>89063</v>
+      </c>
+      <c r="W109">
+        <v>27146.4</v>
+      </c>
+      <c r="X109">
+        <v>417</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z109">
+        <v>12</v>
+      </c>
+      <c r="AA109">
+        <v>3.66</v>
+      </c>
+      <c r="AB109">
+        <v>0.77</v>
+      </c>
+      <c r="AC109">
+        <v>1.7</v>
+      </c>
+      <c r="AD109">
+        <v>54.17</v>
+      </c>
+      <c r="AE109">
+        <v>33.66</v>
+      </c>
+      <c r="AF109" t="s">
+        <v>593</v>
+      </c>
+      <c r="AG109">
+        <v>1.5</v>
+      </c>
+      <c r="AH109">
+        <v>3.31</v>
+      </c>
+      <c r="AI109">
+        <v>3.7</v>
+      </c>
+      <c r="AJ109">
+        <v>8.16</v>
+      </c>
+      <c r="AK109">
+        <v>1.61</v>
+      </c>
+      <c r="AL109">
+        <v>3.54</v>
+      </c>
+      <c r="AM109">
+        <v>7.57</v>
+      </c>
+      <c r="AN109">
+        <v>16.7</v>
+      </c>
+      <c r="AO109">
+        <v>8.35</v>
+      </c>
+      <c r="AP109">
+        <v>18.4</v>
+      </c>
+      <c r="AQ109">
+        <v>6.07</v>
+      </c>
+      <c r="AR109">
+        <v>13.39</v>
+      </c>
+      <c r="AS109">
+        <v>0.77</v>
+      </c>
+      <c r="AT109">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:46">
+      <c r="A110" t="s">
+        <v>62</v>
+      </c>
+      <c r="B110" t="s">
+        <v>594</v>
+      </c>
+      <c r="C110" t="s">
+        <v>589</v>
+      </c>
+      <c r="D110">
+        <v>87335</v>
+      </c>
+      <c r="E110">
+        <v>26619.71</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>595</v>
+      </c>
+      <c r="H110" t="s">
+        <v>286</v>
+      </c>
+      <c r="I110">
+        <v>6390</v>
+      </c>
+      <c r="J110" t="s">
+        <v>258</v>
+      </c>
+      <c r="K110">
+        <v>8061</v>
+      </c>
+      <c r="L110">
+        <v>2456.99</v>
+      </c>
+      <c r="M110">
+        <v>54.36</v>
+      </c>
+      <c r="N110">
+        <v>33.78</v>
+      </c>
+      <c r="O110">
+        <v>39.261833333333335</v>
+      </c>
+      <c r="P110">
+        <v>-103.5945</v>
+      </c>
+      <c r="Q110">
+        <v>5202</v>
+      </c>
+      <c r="R110">
+        <v>1585.57</v>
+      </c>
+      <c r="S110">
+        <v>39.608</v>
+      </c>
+      <c r="T110">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U110" t="s">
+        <v>118</v>
+      </c>
+      <c r="V110">
+        <v>87123</v>
+      </c>
+      <c r="W110">
+        <v>26555.09</v>
+      </c>
+      <c r="X110">
+        <v>409</v>
+      </c>
+      <c r="Y110" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z110">
+        <v>12</v>
+      </c>
+      <c r="AA110">
+        <v>3.66</v>
+      </c>
+      <c r="AB110">
+        <v>0.82</v>
+      </c>
+      <c r="AC110">
+        <v>1.81</v>
+      </c>
+      <c r="AD110">
+        <v>54.36</v>
+      </c>
+      <c r="AE110">
+        <v>33.78</v>
+      </c>
+      <c r="AF110" t="s">
+        <v>596</v>
+      </c>
+      <c r="AG110">
+        <v>1.5</v>
+      </c>
+      <c r="AH110">
+        <v>3.31</v>
+      </c>
+      <c r="AI110">
+        <v>3.6</v>
+      </c>
+      <c r="AJ110">
+        <v>7.94</v>
+      </c>
+      <c r="AK110">
+        <v>1.77</v>
+      </c>
+      <c r="AL110">
+        <v>3.9</v>
+      </c>
+      <c r="AM110">
+        <v>7.69</v>
+      </c>
+      <c r="AN110">
+        <v>16.95</v>
+      </c>
+      <c r="AO110">
+        <v>8.5</v>
+      </c>
+      <c r="AP110">
+        <v>18.73</v>
+      </c>
+      <c r="AQ110">
+        <v>6.19</v>
+      </c>
+      <c r="AR110">
+        <v>13.65</v>
+      </c>
+      <c r="AS110">
+        <v>0.82</v>
+      </c>
+      <c r="AT110">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="111" spans="1:46">
+      <c r="A111" t="s">
+        <v>46</v>
+      </c>
+      <c r="B111" t="s">
+        <v>597</v>
+      </c>
+      <c r="C111" t="s">
+        <v>589</v>
+      </c>
+      <c r="D111">
+        <v>107271</v>
+      </c>
+      <c r="E111">
+        <v>32696.2</v>
+      </c>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>598</v>
+      </c>
+      <c r="H111" t="s">
+        <v>599</v>
+      </c>
+      <c r="I111">
+        <v>7980</v>
+      </c>
+      <c r="J111" t="s">
+        <v>600</v>
+      </c>
+      <c r="K111">
+        <v>9380</v>
+      </c>
+      <c r="L111">
+        <v>2859.02</v>
+      </c>
+      <c r="M111">
+        <v>65.13</v>
+      </c>
+      <c r="N111">
+        <v>40.47</v>
+      </c>
+      <c r="O111">
+        <v>39.30533333333333</v>
+      </c>
+      <c r="P111">
+        <v>-103.392</v>
+      </c>
+      <c r="Q111">
+        <v>5206</v>
+      </c>
+      <c r="R111">
+        <v>1586.79</v>
+      </c>
+      <c r="S111">
+        <v>39.608</v>
+      </c>
+      <c r="T111">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U111" t="s">
+        <v>156</v>
+      </c>
+      <c r="V111">
+        <v>107044</v>
+      </c>
+      <c r="W111">
+        <v>32627.01</v>
+      </c>
+      <c r="X111">
+        <v>705</v>
+      </c>
+      <c r="Y111" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z111">
+        <v>12</v>
+      </c>
+      <c r="AA111">
+        <v>3.66</v>
+      </c>
+      <c r="AB111">
+        <v>0.77</v>
+      </c>
+      <c r="AC111">
+        <v>1.7</v>
+      </c>
+      <c r="AD111">
+        <v>65.13</v>
+      </c>
+      <c r="AE111">
+        <v>40.47</v>
+      </c>
+      <c r="AF111" t="s">
+        <v>601</v>
+      </c>
+      <c r="AG111">
+        <v>3</v>
+      </c>
+      <c r="AH111">
+        <v>6.61</v>
+      </c>
+      <c r="AI111">
+        <v>3</v>
+      </c>
+      <c r="AJ111">
+        <v>6.61</v>
+      </c>
+      <c r="AK111">
+        <v>2.08</v>
+      </c>
+      <c r="AL111">
+        <v>4.59</v>
+      </c>
+      <c r="AM111">
+        <v>8.85</v>
+      </c>
+      <c r="AN111">
+        <v>19.51</v>
+      </c>
+      <c r="AO111">
+        <v>7.62</v>
+      </c>
+      <c r="AP111">
+        <v>16.8</v>
+      </c>
+      <c r="AQ111">
+        <v>5.85</v>
+      </c>
+      <c r="AR111">
+        <v>12.9</v>
+      </c>
+      <c r="AS111">
+        <v>0.77</v>
+      </c>
+      <c r="AT111">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="610">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1820,6 +1820,30 @@
   </si>
   <si>
     <t>[{"altitude_ft":41058.0,"altitude_m":12514.48,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>EOSS-401</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":41732.0,"altitude_m":12719.91,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>EOSS-402</t>
+  </si>
+  <si>
+    <t>2hrs 0mins 0secs</t>
+  </si>
+  <si>
+    <t>319</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":40554.0,"altitude_m":12360.86,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2151,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT111"/>
+  <dimension ref="A1:AT113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -17694,6 +17718,286 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="112" spans="1:46">
+      <c r="A112" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" t="s">
+        <v>588</v>
+      </c>
+      <c r="C112" t="s">
+        <v>602</v>
+      </c>
+      <c r="D112">
+        <v>75129</v>
+      </c>
+      <c r="E112">
+        <v>22899.32</v>
+      </c>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>603</v>
+      </c>
+      <c r="H112" t="s">
+        <v>443</v>
+      </c>
+      <c r="I112">
+        <v>6900</v>
+      </c>
+      <c r="J112" t="s">
+        <v>604</v>
+      </c>
+      <c r="K112">
+        <v>4692</v>
+      </c>
+      <c r="L112">
+        <v>1430.12</v>
+      </c>
+      <c r="M112">
+        <v>97.61</v>
+      </c>
+      <c r="N112">
+        <v>60.65</v>
+      </c>
+      <c r="O112">
+        <v>39.30148333333333</v>
+      </c>
+      <c r="P112">
+        <v>-102.97625</v>
+      </c>
+      <c r="Q112">
+        <v>5214</v>
+      </c>
+      <c r="R112">
+        <v>1589.23</v>
+      </c>
+      <c r="S112">
+        <v>39.608183333333336</v>
+      </c>
+      <c r="T112">
+        <v>-104.04228333333332</v>
+      </c>
+      <c r="U112" t="s">
+        <v>156</v>
+      </c>
+      <c r="V112">
+        <v>75055</v>
+      </c>
+      <c r="W112">
+        <v>22876.76</v>
+      </c>
+      <c r="X112">
+        <v>447</v>
+      </c>
+      <c r="Y112" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z112">
+        <v>12</v>
+      </c>
+      <c r="AA112">
+        <v>3.66</v>
+      </c>
+      <c r="AB112">
+        <v>0.77</v>
+      </c>
+      <c r="AC112">
+        <v>1.7</v>
+      </c>
+      <c r="AD112">
+        <v>97.61</v>
+      </c>
+      <c r="AE112">
+        <v>60.65</v>
+      </c>
+      <c r="AF112" t="s">
+        <v>605</v>
+      </c>
+      <c r="AG112">
+        <v>3</v>
+      </c>
+      <c r="AH112">
+        <v>6.61</v>
+      </c>
+      <c r="AI112">
+        <v>3.32</v>
+      </c>
+      <c r="AJ112">
+        <v>7.31</v>
+      </c>
+      <c r="AK112">
+        <v>1.89</v>
+      </c>
+      <c r="AL112">
+        <v>4.16</v>
+      </c>
+      <c r="AM112">
+        <v>8.98</v>
+      </c>
+      <c r="AN112">
+        <v>19.79</v>
+      </c>
+      <c r="AO112">
+        <v>7.77</v>
+      </c>
+      <c r="AP112">
+        <v>17.13</v>
+      </c>
+      <c r="AQ112">
+        <v>5.97</v>
+      </c>
+      <c r="AR112">
+        <v>13.17</v>
+      </c>
+      <c r="AS112">
+        <v>0.77</v>
+      </c>
+      <c r="AT112">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:46">
+      <c r="A113" t="s">
+        <v>46</v>
+      </c>
+      <c r="B113" t="s">
+        <v>594</v>
+      </c>
+      <c r="C113" t="s">
+        <v>602</v>
+      </c>
+      <c r="D113">
+        <v>72643</v>
+      </c>
+      <c r="E113">
+        <v>22141.59</v>
+      </c>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>606</v>
+      </c>
+      <c r="H113" t="s">
+        <v>607</v>
+      </c>
+      <c r="I113">
+        <v>7200</v>
+      </c>
+      <c r="J113" t="s">
+        <v>608</v>
+      </c>
+      <c r="K113">
+        <v>4824</v>
+      </c>
+      <c r="L113">
+        <v>1470.36</v>
+      </c>
+      <c r="M113">
+        <v>104.12</v>
+      </c>
+      <c r="N113">
+        <v>64.7</v>
+      </c>
+      <c r="O113">
+        <v>39.2435</v>
+      </c>
+      <c r="P113">
+        <v>-102.92466666666668</v>
+      </c>
+      <c r="Q113">
+        <v>5216</v>
+      </c>
+      <c r="R113">
+        <v>1589.84</v>
+      </c>
+      <c r="S113">
+        <v>39.608</v>
+      </c>
+      <c r="T113">
+        <v>-104.04216666666666</v>
+      </c>
+      <c r="U113" t="s">
+        <v>156</v>
+      </c>
+      <c r="V113">
+        <v>72570</v>
+      </c>
+      <c r="W113">
+        <v>22119.34</v>
+      </c>
+      <c r="X113">
+        <v>445</v>
+      </c>
+      <c r="Y113" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z113">
+        <v>12</v>
+      </c>
+      <c r="AA113">
+        <v>3.66</v>
+      </c>
+      <c r="AB113">
+        <v>0.77</v>
+      </c>
+      <c r="AC113">
+        <v>1.7</v>
+      </c>
+      <c r="AD113">
+        <v>104.12</v>
+      </c>
+      <c r="AE113">
+        <v>64.7</v>
+      </c>
+      <c r="AF113" t="s">
+        <v>609</v>
+      </c>
+      <c r="AG113">
+        <v>3</v>
+      </c>
+      <c r="AH113">
+        <v>6.61</v>
+      </c>
+      <c r="AI113">
+        <v>3.45</v>
+      </c>
+      <c r="AJ113">
+        <v>7.61</v>
+      </c>
+      <c r="AK113">
+        <v>1.7</v>
+      </c>
+      <c r="AL113">
+        <v>3.74</v>
+      </c>
+      <c r="AM113">
+        <v>8.92</v>
+      </c>
+      <c r="AN113">
+        <v>19.66</v>
+      </c>
+      <c r="AO113">
+        <v>7.7</v>
+      </c>
+      <c r="AP113">
+        <v>16.97</v>
+      </c>
+      <c r="AQ113">
+        <v>5.91</v>
+      </c>
+      <c r="AR113">
+        <v>13.04</v>
+      </c>
+      <c r="AS113">
+        <v>0.77</v>
+      </c>
+      <c r="AT113">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="615">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1844,6 +1844,21 @@
   </si>
   <si>
     <t>[{"altitude_ft":40554.0,"altitude_m":12360.86,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-06-20</t>
+  </si>
+  <si>
+    <t>EOSS-403</t>
+  </si>
+  <si>
+    <t>2hrs 33mins 0secs</t>
+  </si>
+  <si>
+    <t>159</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":43043.0,"altitude_m":13119.51,"transition":"high_to_low"},{"altitude_ft":70973.0,"altitude_m":21632.57,"transition":"low_to_high"}]</t>
   </si>
 </sst>
 </file>
@@ -2175,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT113"/>
+  <dimension ref="A1:AT114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -17998,6 +18013,146 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="114" spans="1:46">
+      <c r="A114" t="s">
+        <v>62</v>
+      </c>
+      <c r="B114" t="s">
+        <v>588</v>
+      </c>
+      <c r="C114" t="s">
+        <v>610</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114" t="b">
+        <v>0</v>
+      </c>
+      <c r="G114" t="s">
+        <v>611</v>
+      </c>
+      <c r="H114" t="s">
+        <v>612</v>
+      </c>
+      <c r="I114">
+        <v>9180</v>
+      </c>
+      <c r="J114" t="s">
+        <v>613</v>
+      </c>
+      <c r="K114">
+        <v>732</v>
+      </c>
+      <c r="L114">
+        <v>223.11</v>
+      </c>
+      <c r="M114">
+        <v>138.73</v>
+      </c>
+      <c r="N114">
+        <v>86.2</v>
+      </c>
+      <c r="O114">
+        <v>40.74828333333333</v>
+      </c>
+      <c r="P114">
+        <v>-91.4728</v>
+      </c>
+      <c r="Q114">
+        <v>863</v>
+      </c>
+      <c r="R114">
+        <v>263.04</v>
+      </c>
+      <c r="S114">
+        <v>41.39435</v>
+      </c>
+      <c r="T114">
+        <v>-92.88985</v>
+      </c>
+      <c r="U114" t="s">
+        <v>118</v>
+      </c>
+      <c r="V114">
+        <v>100442</v>
+      </c>
+      <c r="W114">
+        <v>30614.72</v>
+      </c>
+      <c r="X114">
+        <v>275</v>
+      </c>
+      <c r="Y114" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z114">
+        <v>10</v>
+      </c>
+      <c r="AA114">
+        <v>3.05</v>
+      </c>
+      <c r="AB114">
+        <v>0.66</v>
+      </c>
+      <c r="AC114">
+        <v>1.46</v>
+      </c>
+      <c r="AD114">
+        <v>138.73</v>
+      </c>
+      <c r="AE114">
+        <v>86.2</v>
+      </c>
+      <c r="AF114" t="s">
+        <v>614</v>
+      </c>
+      <c r="AG114">
+        <v>1.5</v>
+      </c>
+      <c r="AH114">
+        <v>3.31</v>
+      </c>
+      <c r="AI114">
+        <v>0.35</v>
+      </c>
+      <c r="AJ114">
+        <v>0.77</v>
+      </c>
+      <c r="AK114">
+        <v>1.61</v>
+      </c>
+      <c r="AL114">
+        <v>3.54</v>
+      </c>
+      <c r="AM114">
+        <v>4.12</v>
+      </c>
+      <c r="AN114">
+        <v>9.08</v>
+      </c>
+      <c r="AO114">
+        <v>3.85</v>
+      </c>
+      <c r="AP114">
+        <v>8.49</v>
+      </c>
+      <c r="AQ114">
+        <v>2.62</v>
+      </c>
+      <c r="AR114">
+        <v>5.77</v>
+      </c>
+      <c r="AS114">
+        <v>0.66</v>
+      </c>
+      <c r="AT114">
+        <v>1.46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="621">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1859,6 +1859,24 @@
   </si>
   <si>
     <t>[{"altitude_ft":43043.0,"altitude_m":13119.51,"transition":"high_to_low"},{"altitude_ft":70973.0,"altitude_m":21632.57,"transition":"low_to_high"}]</t>
+  </si>
+  <si>
+    <t>["KC0D-2","N0JPS","AE0SS-2","K0SCC-13"]</t>
+  </si>
+  <si>
+    <t>2026-07-25</t>
+  </si>
+  <si>
+    <t>EOSS-404</t>
+  </si>
+  <si>
+    <t>5hrs 29mins 57secs</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":56551.0,"altitude_m":17236.74,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2190,7 +2208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT114"/>
+  <dimension ref="A1:AT115"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -18153,6 +18171,146 @@
         <v>1.46</v>
       </c>
     </row>
+    <row r="115" spans="1:46">
+      <c r="A115" t="s">
+        <v>46</v>
+      </c>
+      <c r="B115" t="s">
+        <v>615</v>
+      </c>
+      <c r="C115" t="s">
+        <v>616</v>
+      </c>
+      <c r="D115">
+        <v>67585</v>
+      </c>
+      <c r="E115">
+        <v>20599.91</v>
+      </c>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>617</v>
+      </c>
+      <c r="H115" t="s">
+        <v>618</v>
+      </c>
+      <c r="I115">
+        <v>19797.699</v>
+      </c>
+      <c r="J115" t="s">
+        <v>619</v>
+      </c>
+      <c r="K115">
+        <v>5590</v>
+      </c>
+      <c r="L115">
+        <v>1703.83</v>
+      </c>
+      <c r="M115">
+        <v>0.05</v>
+      </c>
+      <c r="N115">
+        <v>0.03</v>
+      </c>
+      <c r="O115">
+        <v>39.278</v>
+      </c>
+      <c r="P115">
+        <v>-103.496</v>
+      </c>
+      <c r="Q115">
+        <v>5610</v>
+      </c>
+      <c r="R115">
+        <v>1709.93</v>
+      </c>
+      <c r="S115">
+        <v>39.278166666666664</v>
+      </c>
+      <c r="T115">
+        <v>-103.4955</v>
+      </c>
+      <c r="U115" t="s">
+        <v>156</v>
+      </c>
+      <c r="V115">
+        <v>67568</v>
+      </c>
+      <c r="W115">
+        <v>20594.73</v>
+      </c>
+      <c r="X115">
+        <v>77</v>
+      </c>
+      <c r="Y115" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z115">
+        <v>12</v>
+      </c>
+      <c r="AA115">
+        <v>3.66</v>
+      </c>
+      <c r="AB115">
+        <v>0.77</v>
+      </c>
+      <c r="AC115">
+        <v>1.7</v>
+      </c>
+      <c r="AD115">
+        <v>0.05</v>
+      </c>
+      <c r="AE115">
+        <v>0.03</v>
+      </c>
+      <c r="AF115" t="s">
+        <v>620</v>
+      </c>
+      <c r="AG115">
+        <v>3</v>
+      </c>
+      <c r="AH115">
+        <v>6.61</v>
+      </c>
+      <c r="AI115">
+        <v>6.86</v>
+      </c>
+      <c r="AJ115">
+        <v>15.12</v>
+      </c>
+      <c r="AK115">
+        <v>2.58</v>
+      </c>
+      <c r="AL115">
+        <v>5.68</v>
+      </c>
+      <c r="AM115">
+        <v>13.2</v>
+      </c>
+      <c r="AN115">
+        <v>29.11</v>
+      </c>
+      <c r="AO115">
+        <v>12.85</v>
+      </c>
+      <c r="AP115">
+        <v>28.32</v>
+      </c>
+      <c r="AQ115">
+        <v>10.21</v>
+      </c>
+      <c r="AR115">
+        <v>22.5</v>
+      </c>
+      <c r="AS115">
+        <v>0.77</v>
+      </c>
+      <c r="AT115">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -1870,13 +1870,13 @@
     <t>EOSS-404</t>
   </si>
   <si>
-    <t>5hrs 29mins 57secs</t>
+    <t>1hrs 17mins 30secs</t>
   </si>
   <si>
     <t>472</t>
   </si>
   <si>
-    <t>[{"altitude_ft":56551.0,"altitude_m":17236.74,"transition":"high_to_low"}]</t>
+    <t>[{"altitude_ft":56609.0,"altitude_m":17254.42,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -18197,40 +18197,40 @@
         <v>618</v>
       </c>
       <c r="I115">
-        <v>19797.699</v>
+        <v>4650</v>
       </c>
       <c r="J115" t="s">
         <v>619</v>
       </c>
       <c r="K115">
-        <v>5590</v>
+        <v>6001</v>
       </c>
       <c r="L115">
-        <v>1703.83</v>
+        <v>1829.1</v>
       </c>
       <c r="M115">
-        <v>0.05</v>
+        <v>17.61</v>
       </c>
       <c r="N115">
-        <v>0.03</v>
+        <v>10.94</v>
       </c>
       <c r="O115">
-        <v>39.278</v>
+        <v>39.18613333333333</v>
       </c>
       <c r="P115">
-        <v>-103.496</v>
+        <v>-103.32883333333334</v>
       </c>
       <c r="Q115">
-        <v>5610</v>
+        <v>5606</v>
       </c>
       <c r="R115">
-        <v>1709.93</v>
+        <v>1708.71</v>
       </c>
       <c r="S115">
         <v>39.278166666666664</v>
       </c>
       <c r="T115">
-        <v>-103.4955</v>
+        <v>-103.49533333333332</v>
       </c>
       <c r="U115" t="s">
         <v>156</v>
@@ -18242,7 +18242,7 @@
         <v>20594.73</v>
       </c>
       <c r="X115">
-        <v>77</v>
+        <v>406</v>
       </c>
       <c r="Y115" t="s">
         <v>53</v>
@@ -18260,10 +18260,10 @@
         <v>1.7</v>
       </c>
       <c r="AD115">
-        <v>0.05</v>
+        <v>17.61</v>
       </c>
       <c r="AE115">
-        <v>0.03</v>
+        <v>10.94</v>
       </c>
       <c r="AF115" t="s">
         <v>620</v>

--- a/output/xlsx/flights_metadata.xlsx
+++ b/output/xlsx/flights_metadata.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="625">
   <si>
     <t>balloonsize</t>
   </si>
@@ -1877,6 +1877,18 @@
   </si>
   <si>
     <t>[{"altitude_ft":56609.0,"altitude_m":17254.42,"transition":"high_to_low"}]</t>
+  </si>
+  <si>
+    <t>2026-08-22</t>
+  </si>
+  <si>
+    <t>EOSS-405</t>
+  </si>
+  <si>
+    <t>342</t>
+  </si>
+  <si>
+    <t>[{"altitude_ft":10113.0,"altitude_m":3082.44,"transition":"low_to_high"},{"altitude_ft":61473.0,"altitude_m":18736.97,"transition":"high_to_low"}]</t>
   </si>
 </sst>
 </file>
@@ -2208,7 +2220,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT115"/>
+  <dimension ref="A1:AT116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:46">
@@ -18311,6 +18323,146 @@
         <v>1.7</v>
       </c>
     </row>
+    <row r="116" spans="1:46">
+      <c r="A116" t="s">
+        <v>46</v>
+      </c>
+      <c r="B116" t="s">
+        <v>588</v>
+      </c>
+      <c r="C116" t="s">
+        <v>621</v>
+      </c>
+      <c r="D116">
+        <v>107526</v>
+      </c>
+      <c r="E116">
+        <v>32773.92</v>
+      </c>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>622</v>
+      </c>
+      <c r="H116" t="s">
+        <v>272</v>
+      </c>
+      <c r="I116">
+        <v>7470</v>
+      </c>
+      <c r="J116" t="s">
+        <v>623</v>
+      </c>
+      <c r="K116">
+        <v>5467</v>
+      </c>
+      <c r="L116">
+        <v>1666.34</v>
+      </c>
+      <c r="M116">
+        <v>27.02</v>
+      </c>
+      <c r="N116">
+        <v>16.79</v>
+      </c>
+      <c r="O116">
+        <v>38.993833333333335</v>
+      </c>
+      <c r="P116">
+        <v>-103.72301666666668</v>
+      </c>
+      <c r="Q116">
+        <v>5408</v>
+      </c>
+      <c r="R116">
+        <v>1648.36</v>
+      </c>
+      <c r="S116">
+        <v>39.23613333333333</v>
+      </c>
+      <c r="T116">
+        <v>-103.69696666666668</v>
+      </c>
+      <c r="U116" t="s">
+        <v>156</v>
+      </c>
+      <c r="V116">
+        <v>106755</v>
+      </c>
+      <c r="W116">
+        <v>32538.92</v>
+      </c>
+      <c r="X116">
+        <v>425</v>
+      </c>
+      <c r="Y116" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z116">
+        <v>12</v>
+      </c>
+      <c r="AA116">
+        <v>3.66</v>
+      </c>
+      <c r="AB116">
+        <v>0.77</v>
+      </c>
+      <c r="AC116">
+        <v>1.7</v>
+      </c>
+      <c r="AD116">
+        <v>27.02</v>
+      </c>
+      <c r="AE116">
+        <v>16.79</v>
+      </c>
+      <c r="AF116" t="s">
+        <v>624</v>
+      </c>
+      <c r="AG116">
+        <v>3</v>
+      </c>
+      <c r="AH116">
+        <v>6.61</v>
+      </c>
+      <c r="AI116">
+        <v>3.72</v>
+      </c>
+      <c r="AJ116">
+        <v>8.21</v>
+      </c>
+      <c r="AK116">
+        <v>2.08</v>
+      </c>
+      <c r="AL116">
+        <v>4.58</v>
+      </c>
+      <c r="AM116">
+        <v>9.57</v>
+      </c>
+      <c r="AN116">
+        <v>21.1</v>
+      </c>
+      <c r="AO116">
+        <v>8.48</v>
+      </c>
+      <c r="AP116">
+        <v>18.7</v>
+      </c>
+      <c r="AQ116">
+        <v>6.57</v>
+      </c>
+      <c r="AR116">
+        <v>14.48</v>
+      </c>
+      <c r="AS116">
+        <v>0.77</v>
+      </c>
+      <c r="AT116">
+        <v>1.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
